--- a/nr-prepare-release/ig/StructureDefinition-mesures-diabetis-type.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-mesures-diabetis-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.2-ballot</t>
+    <t>3.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T14:37:47+00:00</t>
+    <t>2024-06-04T11:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release/ig/StructureDefinition-mesures-diabetis-type.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-mesures-diabetis-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T11:28:10+00:00</t>
+    <t>2024-06-04T11:34:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release/ig/StructureDefinition-mesures-diabetis-type.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-mesures-diabetis-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T11:34:57+00:00</t>
+    <t>2024-06-04T14:17:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
